--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:36</t>
+    <t xml:space="preserve">2026-09-09 22:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:22</t>
+    <t xml:space="preserve">2026-09-12 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:39</t>
+    <t xml:space="preserve">2026-09-24 00:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:16</t>
+    <t xml:space="preserve">2026-09-27 22:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:06</t>
+    <t xml:space="preserve">2026-09-29 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,7 +544,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>34.91</v>
+        <v>349.14</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>31.23</v>
+        <v>312.26</v>
       </c>
     </row>
     <row r="4">
@@ -578,7 +578,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.69</v>
+        <v>286.86</v>
       </c>
     </row>
     <row r="5">
@@ -595,7 +595,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>27.46</v>
+        <v>274.57</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>24.96</v>
+        <v>249.62</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>23.23</v>
+        <v>232.34</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20.78</v>
+        <v>207.85</v>
       </c>
     </row>
     <row r="9">
@@ -663,7 +663,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>19.26</v>
+        <v>192.57</v>
       </c>
     </row>
     <row r="10">
@@ -680,7 +680,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>18.42</v>
+        <v>184.16</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>17.81</v>
+        <v>178.14</v>
       </c>
     </row>
     <row r="12">
@@ -714,7 +714,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>17.76</v>
+        <v>177.57</v>
       </c>
     </row>
     <row r="13">
@@ -731,7 +731,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17.59</v>
+        <v>175.92</v>
       </c>
     </row>
     <row r="14">
@@ -748,7 +748,7 @@
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17.43</v>
+        <v>174.34</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>17.25</v>
+        <v>172.47</v>
       </c>
     </row>
     <row r="16">
@@ -782,7 +782,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16.87</v>
+        <v>168.68</v>
       </c>
     </row>
     <row r="17">
@@ -799,7 +799,7 @@
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16.78</v>
+        <v>167.84</v>
       </c>
     </row>
     <row r="18">
@@ -816,7 +816,7 @@
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16.65</v>
+        <v>166.47</v>
       </c>
     </row>
     <row r="19">
@@ -833,7 +833,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15.31</v>
+        <v>153.05</v>
       </c>
     </row>
     <row r="20">
@@ -850,7 +850,7 @@
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>14.69</v>
+        <v>146.88</v>
       </c>
     </row>
     <row r="21">
@@ -867,7 +867,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14.6</v>
+        <v>145.95</v>
       </c>
     </row>
     <row r="22">
@@ -884,7 +884,7 @@
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>14.23</v>
+        <v>142.29</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:00</t>
+    <t xml:space="preserve">2026-10-01 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:25</t>
+    <t xml:space="preserve">2026-10-02 13:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">San Ignacio</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:15</t>
+    <t xml:space="preserve">2026-10-04 07:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:55</t>
+    <t xml:space="preserve">2026-10-05 07:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
